--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FD4FDA-6202-4855-A3D9-0301C3044DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AE2D1C-8026-44BA-96C9-C8639B715040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28268" yWindow="17017" windowWidth="16274" windowHeight="13103" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="3000" windowWidth="21758" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</t>
   </si>
@@ -74,10 +74,6 @@
   </si>
   <si>
     <t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</t>
-  </si>
-  <si>
-    <t>mob_bear</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>곰</t>
@@ -106,9 +102,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2DObject/MonsterSlime</t>
-  </si>
-  <si>
     <t>2DObject/Monster_Bear</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -162,6 +155,34 @@
   </si>
   <si>
     <t>PrefabPath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_bear_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_bat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_helldog_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_frog_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_eagle_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_vulture_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_Slime</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -794,13 +815,13 @@
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>15</v>
@@ -820,16 +841,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>6</v>
@@ -849,22 +870,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29.25" customHeight="1">
@@ -890,10 +911,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.149999999999999" customHeight="1">
@@ -920,13 +941,13 @@
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="4">
         <v>1000</v>
@@ -938,38 +959,48 @@
         <v>100</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="14"/>
+      <c r="A8" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="14"/>
+      <c r="A9" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="14"/>
+      <c r="A12" s="14" t="s">
+        <v>41</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="15"/>
       <c r="E12" s="1"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AE2D1C-8026-44BA-96C9-C8639B715040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F416644-4B7C-4B4B-B56C-F6E7A69FB651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="3000" windowWidth="21758" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="1958" windowWidth="23790" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</t>
   </si>
@@ -183,6 +183,22 @@
   </si>
   <si>
     <t>2DObject/Monster_Slime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쥐</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 박쥐. </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥견</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥에서 올라온 개. 강하다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -956,7 +972,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>32</v>
@@ -972,15 +988,32 @@
       <c r="A8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
+      <c r="B9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="4">
+        <v>200</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F416644-4B7C-4B4B-B56C-F6E7A69FB651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6E2ACF-9C29-4101-B3C1-5EF6CC8BC2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="1958" windowWidth="23790" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</t>
   </si>
@@ -162,10 +162,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>mob_bat_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>mob_helldog_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -182,24 +178,34 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>지옥견</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥에서 올라온 개. 강하다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>2DObject/Monster_Slime</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>박쥐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 박쥐. </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지옥견</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지옥에서 올라온 개. 강하다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>귀엽지만 강한 힘을 가졌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_pigslime_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>피그 슬라임</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_PigSlime</t>
+  </si>
+  <si>
+    <t>2DObject/Monster_HellDog</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.149999999999999" customHeight="1">
@@ -986,24 +992,39 @@
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>44</v>
       </c>
+      <c r="D8" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E8" s="4">
+        <v>150</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4">
         <v>2000</v>
@@ -1014,17 +1035,23 @@
       <c r="F9" s="4">
         <v>3</v>
       </c>
+      <c r="G9" s="4">
+        <v>3</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
@@ -1032,7 +1059,7 @@
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="15"/>
